--- a/tests/data/output/test_report_HMRC_bed_and_breakfast.xlsx
+++ b/tests/data/output/test_report_HMRC_bed_and_breakfast.xlsx
@@ -1159,7 +1159,7 @@
         <v>60.00</v>
       </c>
       <c r="O42" s="7">
-        <v>0</v>
+        <v>0E-28</v>
       </c>
       <c r="P42" s="6">
         <v>2500</v>
@@ -1171,7 +1171,7 @@
         <v>50.0</v>
       </c>
       <c r="S42" s="7">
-        <v>10.00</v>
+        <v>10.00000000000000</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -1206,7 +1206,7 @@
         <v>144.00</v>
       </c>
       <c r="O43" s="7">
-        <v>0</v>
+        <v>0E-28</v>
       </c>
       <c r="P43" s="6">
         <v>1300</v>
@@ -1218,7 +1218,7 @@
         <v>120.0000</v>
       </c>
       <c r="S43" s="7">
-        <v>24.0000</v>
+        <v>24.00000000000000</v>
       </c>
       <c r="T43" s="6">
         <v>1</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="8">
-        <v>1170.0000</v>
+        <v>1170.000000000000</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -1324,7 +1324,7 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="8">
-        <v>234.0000</v>
+        <v>234.0000000000000</v>
       </c>
     </row>
     <row r="57" spans="1:1">
